--- a/benchmarks/results/plots/results-LockdownStats-ROLD.xlsx
+++ b/benchmarks/results/plots/results-LockdownStats-ROLD.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE161"/>
+  <dimension ref="A1:CE182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40960,6 +40960,5277 @@
         <v>28</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=dynamic_gradient</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>18.22222222222222</v>
+      </c>
+      <c r="G162" t="n">
+        <v>18.20925925925926</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>42</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>90</v>
+      </c>
+      <c r="P162" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>42</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=dynamic_gradient</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>8</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>19.51851851851852</v>
+      </c>
+      <c r="G163" t="n">
+        <v>19.51851851851852</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>56</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>90</v>
+      </c>
+      <c r="P163" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>42</v>
+      </c>
+      <c r="U163" t="n">
+        <v>56</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>56</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>42</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>56</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=dynamic_gradient</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>7</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>19.51851851851852</v>
+      </c>
+      <c r="G164" t="n">
+        <v>19.50555555555556</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>56</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>90</v>
+      </c>
+      <c r="P164" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>42</v>
+      </c>
+      <c r="U164" t="n">
+        <v>56</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>56</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>41.30000000000003</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>56</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10.6202749795514</v>
+      </c>
+      <c r="H165" t="n">
+        <v>70</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="n">
+        <v>70</v>
+      </c>
+      <c r="S165" t="n">
+        <v>70</v>
+      </c>
+      <c r="T165" t="n">
+        <v>70</v>
+      </c>
+      <c r="U165" t="n">
+        <v>70</v>
+      </c>
+      <c r="V165" t="n">
+        <v>70</v>
+      </c>
+      <c r="W165" t="n">
+        <v>70</v>
+      </c>
+      <c r="X165" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>63.72164987730839</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>8</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="G166" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="H166" t="n">
+        <v>70</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="n">
+        <v>70</v>
+      </c>
+      <c r="S166" t="n">
+        <v>70</v>
+      </c>
+      <c r="T166" t="n">
+        <v>70</v>
+      </c>
+      <c r="U166" t="n">
+        <v>70</v>
+      </c>
+      <c r="V166" t="n">
+        <v>70</v>
+      </c>
+      <c r="W166" t="n">
+        <v>70</v>
+      </c>
+      <c r="X166" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>7</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>14</v>
+      </c>
+      <c r="G167" t="n">
+        <v>10.7728603878022</v>
+      </c>
+      <c r="H167" t="n">
+        <v>84</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="n">
+        <v>84</v>
+      </c>
+      <c r="S167" t="n">
+        <v>84</v>
+      </c>
+      <c r="T167" t="n">
+        <v>84</v>
+      </c>
+      <c r="U167" t="n">
+        <v>84</v>
+      </c>
+      <c r="V167" t="n">
+        <v>84</v>
+      </c>
+      <c r="W167" t="n">
+        <v>84</v>
+      </c>
+      <c r="X167" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>64.63716232681317</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>145</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>21</v>
+      </c>
+      <c r="G168" t="n">
+        <v>21</v>
+      </c>
+      <c r="H168" t="n">
+        <v>42</v>
+      </c>
+      <c r="I168" t="n">
+        <v>28</v>
+      </c>
+      <c r="J168" t="n">
+        <v>28</v>
+      </c>
+      <c r="K168" t="n">
+        <v>28</v>
+      </c>
+      <c r="L168" t="n">
+        <v>28</v>
+      </c>
+      <c r="M168" t="n">
+        <v>28</v>
+      </c>
+      <c r="N168" t="n">
+        <v>28</v>
+      </c>
+      <c r="O168" t="n">
+        <v>28</v>
+      </c>
+      <c r="P168" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="n">
+        <v>42</v>
+      </c>
+      <c r="S168" t="n">
+        <v>42</v>
+      </c>
+      <c r="T168" t="n">
+        <v>42</v>
+      </c>
+      <c r="U168" t="n">
+        <v>42</v>
+      </c>
+      <c r="V168" t="n">
+        <v>42</v>
+      </c>
+      <c r="W168" t="n">
+        <v>42</v>
+      </c>
+      <c r="X168" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT168" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD168" t="n">
+        <v>28</v>
+      </c>
+      <c r="CE168" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>95</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="G169" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="H169" t="n">
+        <v>42</v>
+      </c>
+      <c r="I169" t="n">
+        <v>28</v>
+      </c>
+      <c r="J169" t="n">
+        <v>28</v>
+      </c>
+      <c r="K169" t="n">
+        <v>28</v>
+      </c>
+      <c r="L169" t="n">
+        <v>28</v>
+      </c>
+      <c r="M169" t="n">
+        <v>28</v>
+      </c>
+      <c r="N169" t="n">
+        <v>28</v>
+      </c>
+      <c r="O169" t="n">
+        <v>28</v>
+      </c>
+      <c r="P169" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="n">
+        <v>42</v>
+      </c>
+      <c r="S169" t="n">
+        <v>42</v>
+      </c>
+      <c r="T169" t="n">
+        <v>42</v>
+      </c>
+      <c r="U169" t="n">
+        <v>42</v>
+      </c>
+      <c r="V169" t="n">
+        <v>42</v>
+      </c>
+      <c r="W169" t="n">
+        <v>42</v>
+      </c>
+      <c r="X169" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>14</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>75</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="G170" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="H170" t="n">
+        <v>70</v>
+      </c>
+      <c r="I170" t="n">
+        <v>14</v>
+      </c>
+      <c r="J170" t="n">
+        <v>14</v>
+      </c>
+      <c r="K170" t="n">
+        <v>14</v>
+      </c>
+      <c r="L170" t="n">
+        <v>14</v>
+      </c>
+      <c r="M170" t="n">
+        <v>14</v>
+      </c>
+      <c r="N170" t="n">
+        <v>14</v>
+      </c>
+      <c r="O170" t="n">
+        <v>14</v>
+      </c>
+      <c r="P170" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="n">
+        <v>70</v>
+      </c>
+      <c r="S170" t="n">
+        <v>70</v>
+      </c>
+      <c r="T170" t="n">
+        <v>70</v>
+      </c>
+      <c r="U170" t="n">
+        <v>70</v>
+      </c>
+      <c r="V170" t="n">
+        <v>70</v>
+      </c>
+      <c r="W170" t="n">
+        <v>70</v>
+      </c>
+      <c r="X170" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD170" t="n">
+        <v>14</v>
+      </c>
+      <c r="CE170" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>55</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>21</v>
+      </c>
+      <c r="G171" t="n">
+        <v>21</v>
+      </c>
+      <c r="H171" t="n">
+        <v>70</v>
+      </c>
+      <c r="I171" t="n">
+        <v>14</v>
+      </c>
+      <c r="J171" t="n">
+        <v>14</v>
+      </c>
+      <c r="K171" t="n">
+        <v>14</v>
+      </c>
+      <c r="L171" t="n">
+        <v>14</v>
+      </c>
+      <c r="M171" t="n">
+        <v>14</v>
+      </c>
+      <c r="N171" t="n">
+        <v>14</v>
+      </c>
+      <c r="O171" t="n">
+        <v>14</v>
+      </c>
+      <c r="P171" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="n">
+        <v>70</v>
+      </c>
+      <c r="S171" t="n">
+        <v>70</v>
+      </c>
+      <c r="T171" t="n">
+        <v>70</v>
+      </c>
+      <c r="U171" t="n">
+        <v>70</v>
+      </c>
+      <c r="V171" t="n">
+        <v>70</v>
+      </c>
+      <c r="W171" t="n">
+        <v>70</v>
+      </c>
+      <c r="X171" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS171" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT171" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD171" t="n">
+        <v>14</v>
+      </c>
+      <c r="CE171" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=activity_gradient_targetGroups=False_targetAct=True_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>155</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>21</v>
+      </c>
+      <c r="G172" t="n">
+        <v>21</v>
+      </c>
+      <c r="H172" t="n">
+        <v>42</v>
+      </c>
+      <c r="I172" t="n">
+        <v>28</v>
+      </c>
+      <c r="J172" t="n">
+        <v>28</v>
+      </c>
+      <c r="K172" t="n">
+        <v>28</v>
+      </c>
+      <c r="L172" t="n">
+        <v>28</v>
+      </c>
+      <c r="M172" t="n">
+        <v>28</v>
+      </c>
+      <c r="N172" t="n">
+        <v>28</v>
+      </c>
+      <c r="O172" t="n">
+        <v>28</v>
+      </c>
+      <c r="P172" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="n">
+        <v>42</v>
+      </c>
+      <c r="S172" t="n">
+        <v>42</v>
+      </c>
+      <c r="T172" t="n">
+        <v>42</v>
+      </c>
+      <c r="U172" t="n">
+        <v>42</v>
+      </c>
+      <c r="V172" t="n">
+        <v>42</v>
+      </c>
+      <c r="W172" t="n">
+        <v>42</v>
+      </c>
+      <c r="X172" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD172" t="n">
+        <v>28</v>
+      </c>
+      <c r="CE172" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>60</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>12.96296296296296</v>
+      </c>
+      <c r="G173" t="n">
+        <v>12.83333333333333</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>28</v>
+      </c>
+      <c r="J173" t="n">
+        <v>28</v>
+      </c>
+      <c r="K173" t="n">
+        <v>14</v>
+      </c>
+      <c r="L173" t="n">
+        <v>14</v>
+      </c>
+      <c r="M173" t="n">
+        <v>14</v>
+      </c>
+      <c r="N173" t="n">
+        <v>14</v>
+      </c>
+      <c r="O173" t="n">
+        <v>14</v>
+      </c>
+      <c r="P173" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="n">
+        <v>28</v>
+      </c>
+      <c r="S173" t="n">
+        <v>28</v>
+      </c>
+      <c r="T173" t="n">
+        <v>14</v>
+      </c>
+      <c r="U173" t="n">
+        <v>14</v>
+      </c>
+      <c r="V173" t="n">
+        <v>14</v>
+      </c>
+      <c r="W173" t="n">
+        <v>14</v>
+      </c>
+      <c r="X173" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT173" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="BW173" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="BX173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY173" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ173" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA173" t="n">
+        <v>14</v>
+      </c>
+      <c r="CB173" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC173" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE173" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="G174" t="n">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>14</v>
+      </c>
+      <c r="K174" t="n">
+        <v>14</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>14</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>14</v>
+      </c>
+      <c r="T174" t="n">
+        <v>14</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX174" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB174" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>8</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="G175" t="n">
+        <v>10.52774217912566</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>14</v>
+      </c>
+      <c r="J175" t="n">
+        <v>28</v>
+      </c>
+      <c r="K175" t="n">
+        <v>14</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>42</v>
+      </c>
+      <c r="P175" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="n">
+        <v>14</v>
+      </c>
+      <c r="S175" t="n">
+        <v>28</v>
+      </c>
+      <c r="T175" t="n">
+        <v>14</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" t="n">
+        <v>0</v>
+      </c>
+      <c r="X175" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>29.69961553455713</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>29.69961553455713</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>29.69961553455713</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ175" t="n">
+        <v>42</v>
+      </c>
+      <c r="BR175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW175" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB175" t="n">
+        <v>29.69961553455713</v>
+      </c>
+      <c r="CC175" t="n">
+        <v>28</v>
+      </c>
+      <c r="CD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE175" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>35</v>
+      </c>
+      <c r="C176" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>16.11111111111111</v>
+      </c>
+      <c r="G176" t="n">
+        <v>16.11111111111111</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>28</v>
+      </c>
+      <c r="J176" t="n">
+        <v>42</v>
+      </c>
+      <c r="K176" t="n">
+        <v>14</v>
+      </c>
+      <c r="L176" t="n">
+        <v>14</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>28</v>
+      </c>
+      <c r="P176" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="n">
+        <v>28</v>
+      </c>
+      <c r="S176" t="n">
+        <v>42</v>
+      </c>
+      <c r="T176" t="n">
+        <v>14</v>
+      </c>
+      <c r="U176" t="n">
+        <v>14</v>
+      </c>
+      <c r="V176" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" t="n">
+        <v>0</v>
+      </c>
+      <c r="X176" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>48</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>48</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>42</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BR176" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV176" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW176" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB176" t="n">
+        <v>28</v>
+      </c>
+      <c r="CC176" t="n">
+        <v>48</v>
+      </c>
+      <c r="CD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE176" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>7</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5.185185185185185</v>
+      </c>
+      <c r="G177" t="n">
+        <v>5.185185185185185</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>14</v>
+      </c>
+      <c r="K177" t="n">
+        <v>14</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>14</v>
+      </c>
+      <c r="T177" t="n">
+        <v>14</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>0</v>
+      </c>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR177" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC177" t="n">
+        <v>28</v>
+      </c>
+      <c r="CD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>145</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>16.85185185185185</v>
+      </c>
+      <c r="G178" t="n">
+        <v>16.72222222222222</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>28</v>
+      </c>
+      <c r="J178" t="n">
+        <v>28</v>
+      </c>
+      <c r="K178" t="n">
+        <v>28</v>
+      </c>
+      <c r="L178" t="n">
+        <v>28</v>
+      </c>
+      <c r="M178" t="n">
+        <v>28</v>
+      </c>
+      <c r="N178" t="n">
+        <v>14</v>
+      </c>
+      <c r="O178" t="n">
+        <v>14</v>
+      </c>
+      <c r="P178" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="n">
+        <v>28</v>
+      </c>
+      <c r="S178" t="n">
+        <v>28</v>
+      </c>
+      <c r="T178" t="n">
+        <v>28</v>
+      </c>
+      <c r="U178" t="n">
+        <v>28</v>
+      </c>
+      <c r="V178" t="n">
+        <v>28</v>
+      </c>
+      <c r="W178" t="n">
+        <v>14</v>
+      </c>
+      <c r="X178" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>26.59999999999999</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>26.59999999999999</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>26.59999999999999</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>26.59999999999999</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>14</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>26.59999999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>165</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="G179" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>28</v>
+      </c>
+      <c r="J179" t="n">
+        <v>28</v>
+      </c>
+      <c r="K179" t="n">
+        <v>28</v>
+      </c>
+      <c r="L179" t="n">
+        <v>28</v>
+      </c>
+      <c r="M179" t="n">
+        <v>28</v>
+      </c>
+      <c r="N179" t="n">
+        <v>28</v>
+      </c>
+      <c r="O179" t="n">
+        <v>14</v>
+      </c>
+      <c r="P179" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="n">
+        <v>28</v>
+      </c>
+      <c r="S179" t="n">
+        <v>28</v>
+      </c>
+      <c r="T179" t="n">
+        <v>28</v>
+      </c>
+      <c r="U179" t="n">
+        <v>28</v>
+      </c>
+      <c r="V179" t="n">
+        <v>28</v>
+      </c>
+      <c r="W179" t="n">
+        <v>28</v>
+      </c>
+      <c r="X179" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>115</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="G180" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>28</v>
+      </c>
+      <c r="J180" t="n">
+        <v>28</v>
+      </c>
+      <c r="K180" t="n">
+        <v>28</v>
+      </c>
+      <c r="L180" t="n">
+        <v>28</v>
+      </c>
+      <c r="M180" t="n">
+        <v>28</v>
+      </c>
+      <c r="N180" t="n">
+        <v>28</v>
+      </c>
+      <c r="O180" t="n">
+        <v>14</v>
+      </c>
+      <c r="P180" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="n">
+        <v>28</v>
+      </c>
+      <c r="S180" t="n">
+        <v>28</v>
+      </c>
+      <c r="T180" t="n">
+        <v>28</v>
+      </c>
+      <c r="U180" t="n">
+        <v>28</v>
+      </c>
+      <c r="V180" t="n">
+        <v>28</v>
+      </c>
+      <c r="W180" t="n">
+        <v>28</v>
+      </c>
+      <c r="X180" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC180" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE180" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>70</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>14.25925925925926</v>
+      </c>
+      <c r="G181" t="n">
+        <v>14.25925925925926</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>28</v>
+      </c>
+      <c r="J181" t="n">
+        <v>28</v>
+      </c>
+      <c r="K181" t="n">
+        <v>28</v>
+      </c>
+      <c r="L181" t="n">
+        <v>28</v>
+      </c>
+      <c r="M181" t="n">
+        <v>14</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>14</v>
+      </c>
+      <c r="P181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="n">
+        <v>28</v>
+      </c>
+      <c r="S181" t="n">
+        <v>28</v>
+      </c>
+      <c r="T181" t="n">
+        <v>28</v>
+      </c>
+      <c r="U181" t="n">
+        <v>28</v>
+      </c>
+      <c r="V181" t="n">
+        <v>14</v>
+      </c>
+      <c r="W181" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>linearization_heuristic_optBouncing=False_initial_uhat=age_group_gradient_targetGroups=True_targetAct=False_targetTests=True</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>125</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="G182" t="n">
+        <v>18.14814814814815</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>28</v>
+      </c>
+      <c r="J182" t="n">
+        <v>28</v>
+      </c>
+      <c r="K182" t="n">
+        <v>28</v>
+      </c>
+      <c r="L182" t="n">
+        <v>28</v>
+      </c>
+      <c r="M182" t="n">
+        <v>28</v>
+      </c>
+      <c r="N182" t="n">
+        <v>28</v>
+      </c>
+      <c r="O182" t="n">
+        <v>14</v>
+      </c>
+      <c r="P182" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="n">
+        <v>28</v>
+      </c>
+      <c r="S182" t="n">
+        <v>28</v>
+      </c>
+      <c r="T182" t="n">
+        <v>28</v>
+      </c>
+      <c r="U182" t="n">
+        <v>28</v>
+      </c>
+      <c r="V182" t="n">
+        <v>28</v>
+      </c>
+      <c r="W182" t="n">
+        <v>28</v>
+      </c>
+      <c r="X182" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ182" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR182" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BU182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ182" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA182" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB182" t="n">
+        <v>14</v>
+      </c>
+      <c r="CC182" t="n">
+        <v>14</v>
+      </c>
+      <c r="CD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE182" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
